--- a/MASTER_RESULTS_APST_MARKOV.xlsx
+++ b/MASTER_RESULTS_APST_MARKOV.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 00:10:10 UTC</t>
+          <t>2026-09-25 20:13:43 UTC</t>
         </is>
       </c>
     </row>
